--- a/FM-MN-07_MIG CO2-01.xlsx
+++ b/FM-MN-07_MIG CO2-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34D59DF-C53E-4E24-81DF-DA875E437C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97F2E20-D341-4F77-9472-B2CE5C826AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>ใบตรวจสอบเครื่อง MIG</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>ตรวจสภาพความพร้อมโดยรวมของเครื่อง</t>
-  </si>
-  <si>
-    <t>/</t>
   </si>
   <si>
     <t>เช็ค BREAKER เพื่อเช็คระบบไฟฟ้า ตามตำแหน่งไฟ โชว์ และสวิชท์ต่าง ๆ</t>
@@ -61,16 +58,7 @@
     <t>ทำความสะอาดหัวเชื่อมก่อนใช้งาน</t>
   </si>
   <si>
-    <t>นายZ</t>
-  </si>
-  <si>
-    <t>พลวัฒน์</t>
-  </si>
-  <si>
     <t>บันทึกเพิ่มเติม</t>
-  </si>
-  <si>
-    <t>เครื่องจักรปกติ</t>
   </si>
   <si>
     <t>ผู้จัดการแผนกซ่อมบำรุง</t>
@@ -442,47 +430,47 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1540,80 +1528,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="15" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="39"/>
+      <c r="AE1" s="39"/>
+      <c r="AF1" s="39"/>
+      <c r="AG1" s="39"/>
     </row>
     <row r="2" spans="1:33" s="15" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="26" t="s">
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39"/>
+      <c r="W2" s="39"/>
+      <c r="X2" s="39"/>
+      <c r="Y2" s="39"/>
+      <c r="Z2" s="39"/>
+      <c r="AA2" s="39"/>
+      <c r="AB2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
+      <c r="AC2" s="39"/>
+      <c r="AD2" s="39"/>
+      <c r="AE2" s="39"/>
+      <c r="AF2" s="39"/>
+      <c r="AG2" s="39"/>
     </row>
     <row r="3" spans="1:33" s="15" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="18"/>
@@ -1651,49 +1639,49 @@
       <c r="AG3" s="16"/>
     </row>
     <row r="4" spans="1:33" s="11" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="36"/>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="36"/>
-      <c r="AB4" s="36"/>
-      <c r="AC4" s="36"/>
-      <c r="AD4" s="36"/>
-      <c r="AE4" s="36"/>
-      <c r="AF4" s="36"/>
-      <c r="AG4" s="37"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="26"/>
+      <c r="W4" s="26"/>
+      <c r="X4" s="26"/>
+      <c r="Y4" s="26"/>
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="26"/>
+      <c r="AC4" s="26"/>
+      <c r="AD4" s="26"/>
+      <c r="AE4" s="26"/>
+      <c r="AF4" s="26"/>
+      <c r="AG4" s="27"/>
     </row>
     <row r="5" spans="1:33" s="11" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="39"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="12">
         <v>1</v>
       </c>
@@ -1819,9 +1807,7 @@
       <c r="X6" s="14"/>
       <c r="Y6" s="14"/>
       <c r="Z6" s="14"/>
-      <c r="AA6" s="14" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA6" s="14"/>
       <c r="AB6" s="14"/>
       <c r="AC6" s="14"/>
       <c r="AD6" s="14"/>
@@ -1834,7 +1820,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -1860,9 +1846,7 @@
       <c r="X7" s="14"/>
       <c r="Y7" s="14"/>
       <c r="Z7" s="14"/>
-      <c r="AA7" s="14" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA7" s="14"/>
       <c r="AB7" s="14"/>
       <c r="AC7" s="14"/>
       <c r="AD7" s="14"/>
@@ -1875,7 +1859,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -1901,9 +1885,7 @@
       <c r="X8" s="14"/>
       <c r="Y8" s="14"/>
       <c r="Z8" s="14"/>
-      <c r="AA8" s="14" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA8" s="14"/>
       <c r="AB8" s="14"/>
       <c r="AC8" s="14"/>
       <c r="AD8" s="14"/>
@@ -1916,7 +1898,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -1942,9 +1924,7 @@
       <c r="X9" s="14"/>
       <c r="Y9" s="14"/>
       <c r="Z9" s="14"/>
-      <c r="AA9" s="14" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA9" s="14"/>
       <c r="AB9" s="14"/>
       <c r="AC9" s="14"/>
       <c r="AD9" s="14"/>
@@ -1957,7 +1937,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -1983,9 +1963,7 @@
       <c r="X10" s="14"/>
       <c r="Y10" s="14"/>
       <c r="Z10" s="14"/>
-      <c r="AA10" s="14" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA10" s="14"/>
       <c r="AB10" s="14"/>
       <c r="AC10" s="14"/>
       <c r="AD10" s="14"/>
@@ -1998,7 +1976,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
@@ -2024,9 +2002,7 @@
       <c r="X11" s="14"/>
       <c r="Y11" s="14"/>
       <c r="Z11" s="14"/>
-      <c r="AA11" s="14" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA11" s="14"/>
       <c r="AB11" s="14"/>
       <c r="AC11" s="14"/>
       <c r="AD11" s="14"/>
@@ -2039,7 +2015,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -2065,9 +2041,7 @@
       <c r="X12" s="14"/>
       <c r="Y12" s="14"/>
       <c r="Z12" s="14"/>
-      <c r="AA12" s="14" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA12" s="14"/>
       <c r="AB12" s="14"/>
       <c r="AC12" s="14"/>
       <c r="AD12" s="14"/>
@@ -2078,172 +2052,166 @@
     <row r="13" spans="1:33" ht="22.5" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="28"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="28"/>
-      <c r="W13" s="28"/>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB13" s="28"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="28"/>
-      <c r="AE13" s="28"/>
-      <c r="AF13" s="28"/>
-      <c r="AG13" s="28"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="32"/>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="33"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="32"/>
+      <c r="AE13" s="32"/>
+      <c r="AF13" s="32"/>
+      <c r="AG13" s="32"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="B14" s="6"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="25"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="25"/>
-      <c r="X14" s="25"/>
-      <c r="Y14" s="25"/>
-      <c r="Z14" s="25"/>
-      <c r="AA14" s="25"/>
-      <c r="AB14" s="25"/>
-      <c r="AC14" s="25"/>
-      <c r="AD14" s="25"/>
-      <c r="AE14" s="25"/>
-      <c r="AF14" s="25"/>
-      <c r="AG14" s="25"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="29"/>
+      <c r="AG14" s="29"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="6"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="24"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="28"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="28"/>
+      <c r="AC15" s="28"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="28"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="6"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25"/>
-      <c r="V16" s="25"/>
-      <c r="W16" s="25"/>
-      <c r="X16" s="25"/>
-      <c r="Y16" s="25"/>
-      <c r="Z16" s="25"/>
-      <c r="AA16" s="25"/>
-      <c r="AB16" s="25"/>
-      <c r="AC16" s="25"/>
-      <c r="AD16" s="25"/>
-      <c r="AE16" s="25"/>
-      <c r="AF16" s="25"/>
-      <c r="AG16" s="25"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="29"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="29"/>
+      <c r="AC16" s="29"/>
+      <c r="AD16" s="29"/>
+      <c r="AE16" s="29"/>
+      <c r="AF16" s="29"/>
+      <c r="AG16" s="29"/>
     </row>
     <row r="17" spans="2:33" ht="19.5" customHeight="1">
       <c r="B17" s="22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:33" ht="211.5" customHeight="1">
-      <c r="B18" s="41" t="s">
-        <v>16</v>
-      </c>
+    <row r="18" spans="2:33" ht="335.25" customHeight="1">
+      <c r="B18" s="24"/>
       <c r="J18" s="23"/>
     </row>
     <row r="19" spans="2:33" ht="21" customHeight="1">
       <c r="AA19" s="5"/>
       <c r="AB19" s="5"/>
-      <c r="AC19" s="34"/>
-      <c r="AD19" s="35"/>
-      <c r="AE19" s="35"/>
-      <c r="AF19" s="35"/>
-      <c r="AG19" s="35"/>
+      <c r="AC19" s="36"/>
+      <c r="AD19" s="37"/>
+      <c r="AE19" s="37"/>
+      <c r="AF19" s="37"/>
+      <c r="AG19" s="37"/>
     </row>
     <row r="20" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC20" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD20" s="32"/>
-      <c r="AE20" s="32"/>
-      <c r="AF20" s="32"/>
-      <c r="AG20" s="32"/>
+      <c r="AC20" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD20" s="35"/>
+      <c r="AE20" s="35"/>
+      <c r="AF20" s="35"/>
+      <c r="AG20" s="35"/>
     </row>
     <row r="21" spans="2:33" ht="7.5" customHeight="1">
       <c r="D21" s="4"/>
@@ -2251,11 +2219,65 @@
     <row r="22" spans="2:33" ht="14.25" customHeight="1">
       <c r="C22" s="3"/>
       <c r="AG22" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="Y15:Y16"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="AA15:AA16"/>
+    <mergeCell ref="AC15:AC16"/>
+    <mergeCell ref="AD15:AD16"/>
+    <mergeCell ref="AF15:AF16"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="AE13:AE14"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="AC20:AG20"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="AC19:AG19"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="AE15:AE16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="AG15:AG16"/>
+    <mergeCell ref="P15:P16"/>
     <mergeCell ref="C4:AG4"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="Z15:Z16"/>
@@ -2272,64 +2294,10 @@
     <mergeCell ref="K15:K16"/>
     <mergeCell ref="O15:O16"/>
     <mergeCell ref="U15:U16"/>
-    <mergeCell ref="AC20:AG20"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="AC19:AG19"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="AE15:AE16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="AG15:AG16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="X15:X16"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="Y15:Y16"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="AD13:AD14"/>
-    <mergeCell ref="AA15:AA16"/>
-    <mergeCell ref="AC15:AC16"/>
-    <mergeCell ref="AD15:AD16"/>
-    <mergeCell ref="AF15:AF16"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="AE13:AE14"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="80" orientation="landscape" horizontalDpi="4294967292"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="80" orientation="landscape" horizontalDpi="4294967292" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/FM-MN-07_MIG CO2-01.xlsx
+++ b/FM-MN-07_MIG CO2-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97F2E20-D341-4F77-9472-B2CE5C826AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81B8EE0-2307-4507-922E-F983FB73065C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -369,7 +369,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -427,50 +427,47 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1528,80 +1525,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="15" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="38" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
     </row>
     <row r="2" spans="1:33" s="15" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="38" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="39"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="26"/>
     </row>
     <row r="3" spans="1:33" s="15" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="18"/>
@@ -1639,49 +1636,49 @@
       <c r="AG3" s="16"/>
     </row>
     <row r="4" spans="1:33" s="11" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="26"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="26"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="26"/>
-      <c r="AE4" s="26"/>
-      <c r="AF4" s="26"/>
-      <c r="AG4" s="27"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="35"/>
+      <c r="AE4" s="35"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="36"/>
     </row>
     <row r="5" spans="1:33" s="11" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="29"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="38"/>
       <c r="C5" s="12">
         <v>1</v>
       </c>
@@ -2052,139 +2049,139 @@
     <row r="13" spans="1:33" ht="22.5" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="32"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="32"/>
-      <c r="U13" s="32"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="32"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="32"/>
-      <c r="AA13" s="33"/>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="32"/>
-      <c r="AE13" s="32"/>
-      <c r="AF13" s="32"/>
-      <c r="AG13" s="32"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="27"/>
+      <c r="AE13" s="27"/>
+      <c r="AF13" s="27"/>
+      <c r="AG13" s="27"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="B14" s="6"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="29"/>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="29"/>
-      <c r="AD14" s="29"/>
-      <c r="AE14" s="29"/>
-      <c r="AF14" s="29"/>
-      <c r="AG14" s="29"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="6"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="28"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="28"/>
-      <c r="X15" s="28"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="28"/>
-      <c r="AA15" s="40"/>
-      <c r="AB15" s="28"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="28"/>
-      <c r="AE15" s="28"/>
-      <c r="AF15" s="28"/>
-      <c r="AG15" s="28"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="23"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="23"/>
+      <c r="AD15" s="23"/>
+      <c r="AE15" s="23"/>
+      <c r="AF15" s="23"/>
+      <c r="AG15" s="23"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="6"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="29"/>
-      <c r="Z16" s="29"/>
-      <c r="AA16" s="29"/>
-      <c r="AB16" s="29"/>
-      <c r="AC16" s="29"/>
-      <c r="AD16" s="29"/>
-      <c r="AE16" s="29"/>
-      <c r="AF16" s="29"/>
-      <c r="AG16" s="29"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
     </row>
     <row r="17" spans="2:33" ht="19.5" customHeight="1">
       <c r="B17" s="22" t="s">
@@ -2192,26 +2189,56 @@
       </c>
     </row>
     <row r="18" spans="2:33" ht="335.25" customHeight="1">
-      <c r="B18" s="24"/>
-      <c r="J18" s="23"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="40"/>
+      <c r="S18" s="40"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
+      <c r="V18" s="40"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="40"/>
+      <c r="Y18" s="40"/>
+      <c r="Z18" s="40"/>
+      <c r="AA18" s="40"/>
+      <c r="AB18" s="40"/>
+      <c r="AC18" s="40"/>
+      <c r="AD18" s="40"/>
+      <c r="AE18" s="40"/>
+      <c r="AF18" s="40"/>
+      <c r="AG18" s="40"/>
     </row>
     <row r="19" spans="2:33" ht="21" customHeight="1">
       <c r="AA19" s="5"/>
       <c r="AB19" s="5"/>
-      <c r="AC19" s="36"/>
-      <c r="AD19" s="37"/>
-      <c r="AE19" s="37"/>
-      <c r="AF19" s="37"/>
-      <c r="AG19" s="37"/>
+      <c r="AC19" s="33"/>
+      <c r="AD19" s="34"/>
+      <c r="AE19" s="34"/>
+      <c r="AF19" s="34"/>
+      <c r="AG19" s="34"/>
     </row>
     <row r="20" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC20" s="34" t="s">
+      <c r="AC20" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="AD20" s="35"/>
-      <c r="AE20" s="35"/>
-      <c r="AF20" s="35"/>
-      <c r="AG20" s="35"/>
+      <c r="AD20" s="31"/>
+      <c r="AE20" s="31"/>
+      <c r="AF20" s="31"/>
+      <c r="AG20" s="31"/>
     </row>
     <row r="21" spans="2:33" ht="7.5" customHeight="1">
       <c r="D21" s="4"/>
@@ -2223,7 +2250,62 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="71">
+    <mergeCell ref="B18:AG18"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="AB15:AB16"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="AF13:AF14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="U15:U16"/>
+    <mergeCell ref="AC20:AG20"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="AC19:AG19"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="AE15:AE16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="AG15:AG16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="W15:W16"/>
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="Y15:Y16"/>
@@ -2240,60 +2322,6 @@
     <mergeCell ref="A1:AA2"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="R15:R16"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="X15:X16"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="AC20:AG20"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="AC19:AG19"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="AE15:AE16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="AG15:AG16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="T15:T16"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="AB15:AB16"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="AF13:AF14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="U15:U16"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_MIG CO2-01.xlsx
+++ b/FM-MN-07_MIG CO2-01.xlsx
@@ -1778,8 +1778,16 @@
       <c r="AB6" s="14" t="n"/>
       <c r="AC6" s="14" t="n"/>
       <c r="AD6" s="14" t="n"/>
-      <c r="AE6" s="14" t="n"/>
-      <c r="AF6" s="14" t="n"/>
+      <c r="AE6" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="14" t="n"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="11">
@@ -1819,8 +1827,16 @@
       <c r="AB7" s="14" t="n"/>
       <c r="AC7" s="14" t="n"/>
       <c r="AD7" s="14" t="n"/>
-      <c r="AE7" s="14" t="n"/>
-      <c r="AF7" s="14" t="n"/>
+      <c r="AE7" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG7" s="14" t="n"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="11">
@@ -1860,8 +1876,16 @@
       <c r="AB8" s="14" t="n"/>
       <c r="AC8" s="14" t="n"/>
       <c r="AD8" s="14" t="n"/>
-      <c r="AE8" s="14" t="n"/>
-      <c r="AF8" s="14" t="n"/>
+      <c r="AE8" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG8" s="14" t="n"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="11">
@@ -1901,8 +1925,16 @@
       <c r="AB9" s="14" t="n"/>
       <c r="AC9" s="14" t="n"/>
       <c r="AD9" s="14" t="n"/>
-      <c r="AE9" s="14" t="n"/>
-      <c r="AF9" s="14" t="n"/>
+      <c r="AE9" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="14" t="n"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="11">
@@ -1942,8 +1974,16 @@
       <c r="AB10" s="14" t="n"/>
       <c r="AC10" s="14" t="n"/>
       <c r="AD10" s="14" t="n"/>
-      <c r="AE10" s="14" t="n"/>
-      <c r="AF10" s="14" t="n"/>
+      <c r="AE10" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="14" t="n"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="11">
@@ -1983,8 +2023,16 @@
       <c r="AB11" s="14" t="n"/>
       <c r="AC11" s="14" t="n"/>
       <c r="AD11" s="14" t="n"/>
-      <c r="AE11" s="14" t="n"/>
-      <c r="AF11" s="14" t="n"/>
+      <c r="AE11" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF11" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG11" s="14" t="n"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="11">
@@ -2024,8 +2072,16 @@
       <c r="AB12" s="14" t="n"/>
       <c r="AC12" s="14" t="n"/>
       <c r="AD12" s="14" t="n"/>
-      <c r="AE12" s="14" t="n"/>
-      <c r="AF12" s="14" t="n"/>
+      <c r="AE12" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF12" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG12" s="14" t="n"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
@@ -2059,8 +2115,16 @@
       <c r="AB13" s="27" t="n"/>
       <c r="AC13" s="27" t="n"/>
       <c r="AD13" s="27" t="n"/>
-      <c r="AE13" s="27" t="n"/>
-      <c r="AF13" s="27" t="n"/>
+      <c r="AE13" s="39" t="inlineStr">
+        <is>
+          <t>ธนุช สิงห์เถื่อน</t>
+        </is>
+      </c>
+      <c r="AF13" s="39" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
       <c r="AG13" s="27" t="n"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -2173,7 +2237,7 @@
       </c>
     </row>
     <row r="18" ht="335.25" customHeight="1">
-      <c r="B18" s="40" t="n"/>
+      <c r="B18" s="40" t="inlineStr"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="AA19" s="5" t="n"/>

--- a/FM-MN-07_MIG CO2-01.xlsx
+++ b/FM-MN-07_MIG CO2-01.xlsx
@@ -1788,7 +1788,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG6" s="14" t="n"/>
+      <c r="AG6" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A7" s="10" t="n">
@@ -1837,7 +1841,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG7" s="14" t="n"/>
+      <c r="AG7" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A8" s="10" t="n">
@@ -1886,7 +1894,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG8" s="14" t="n"/>
+      <c r="AG8" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A9" s="10" t="n">
@@ -1935,7 +1947,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG9" s="14" t="n"/>
+      <c r="AG9" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A10" s="10" t="n">
@@ -1984,7 +2000,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG10" s="14" t="n"/>
+      <c r="AG10" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A11" s="10" t="n">
@@ -2033,7 +2053,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG11" s="14" t="n"/>
+      <c r="AG11" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A12" s="9" t="n">
@@ -2082,7 +2106,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG12" s="14" t="n"/>
+      <c r="AG12" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="8" t="n"/>
@@ -2125,7 +2153,11 @@
           <t>อินทัช เป็นสุข</t>
         </is>
       </c>
-      <c r="AG13" s="27" t="n"/>
+      <c r="AG13" s="39" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="B14" s="6" t="n"/>

--- a/FM-MN-07_MIG CO2-01.xlsx
+++ b/FM-MN-07_MIG CO2-01.xlsx
@@ -340,7 +340,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -439,6 +439,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1750,49 +1753,37 @@
           <t>ตรวจสภาพความพร้อมโดยรวมของเครื่อง</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="14" t="n"/>
-      <c r="I6" s="14" t="n"/>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="14" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="14" t="n"/>
-      <c r="N6" s="14" t="n"/>
-      <c r="O6" s="14" t="n"/>
-      <c r="P6" s="14" t="n"/>
-      <c r="Q6" s="14" t="n"/>
-      <c r="R6" s="14" t="n"/>
-      <c r="S6" s="14" t="n"/>
-      <c r="T6" s="14" t="n"/>
-      <c r="U6" s="14" t="n"/>
-      <c r="V6" s="14" t="n"/>
-      <c r="W6" s="14" t="n"/>
-      <c r="X6" s="14" t="n"/>
-      <c r="Y6" s="14" t="n"/>
-      <c r="Z6" s="14" t="n"/>
-      <c r="AA6" s="14" t="n"/>
-      <c r="AB6" s="14" t="n"/>
-      <c r="AC6" s="14" t="n"/>
-      <c r="AD6" s="14" t="n"/>
-      <c r="AE6" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C6" s="14" t="inlineStr"/>
+      <c r="D6" s="14" t="inlineStr"/>
+      <c r="E6" s="14" t="inlineStr"/>
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="14" t="inlineStr"/>
+      <c r="H6" s="14" t="inlineStr"/>
+      <c r="I6" s="14" t="inlineStr"/>
+      <c r="J6" s="14" t="inlineStr"/>
+      <c r="K6" s="14" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
+      <c r="N6" s="14" t="inlineStr"/>
+      <c r="O6" s="14" t="inlineStr"/>
+      <c r="P6" s="14" t="inlineStr"/>
+      <c r="Q6" s="14" t="inlineStr"/>
+      <c r="R6" s="14" t="inlineStr"/>
+      <c r="S6" s="14" t="inlineStr"/>
+      <c r="T6" s="14" t="inlineStr"/>
+      <c r="U6" s="14" t="inlineStr"/>
+      <c r="V6" s="14" t="inlineStr"/>
+      <c r="W6" s="14" t="inlineStr"/>
+      <c r="X6" s="14" t="inlineStr"/>
+      <c r="Y6" s="14" t="inlineStr"/>
+      <c r="Z6" s="14" t="inlineStr"/>
+      <c r="AA6" s="14" t="inlineStr"/>
+      <c r="AB6" s="14" t="inlineStr"/>
+      <c r="AC6" s="14" t="inlineStr"/>
+      <c r="AD6" s="14" t="inlineStr"/>
+      <c r="AE6" s="14" t="inlineStr"/>
+      <c r="AF6" s="14" t="inlineStr"/>
+      <c r="AG6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A7" s="10" t="n">
@@ -1803,49 +1794,37 @@
           <t>เช็ค BREAKER เพื่อเช็คระบบไฟฟ้า ตามตำแหน่งไฟ โชว์ และสวิชท์ต่าง ๆ</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="14" t="n"/>
-      <c r="I7" s="14" t="n"/>
-      <c r="J7" s="14" t="n"/>
-      <c r="K7" s="14" t="n"/>
-      <c r="L7" s="14" t="n"/>
-      <c r="M7" s="14" t="n"/>
-      <c r="N7" s="14" t="n"/>
-      <c r="O7" s="14" t="n"/>
-      <c r="P7" s="14" t="n"/>
-      <c r="Q7" s="14" t="n"/>
-      <c r="R7" s="14" t="n"/>
-      <c r="S7" s="14" t="n"/>
-      <c r="T7" s="14" t="n"/>
-      <c r="U7" s="14" t="n"/>
-      <c r="V7" s="14" t="n"/>
-      <c r="W7" s="14" t="n"/>
-      <c r="X7" s="14" t="n"/>
-      <c r="Y7" s="14" t="n"/>
-      <c r="Z7" s="14" t="n"/>
-      <c r="AA7" s="14" t="n"/>
-      <c r="AB7" s="14" t="n"/>
-      <c r="AC7" s="14" t="n"/>
-      <c r="AD7" s="14" t="n"/>
-      <c r="AE7" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF7" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG7" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C7" s="14" t="inlineStr"/>
+      <c r="D7" s="14" t="inlineStr"/>
+      <c r="E7" s="14" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr"/>
+      <c r="J7" s="14" t="inlineStr"/>
+      <c r="K7" s="14" t="inlineStr"/>
+      <c r="L7" s="14" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
+      <c r="N7" s="14" t="inlineStr"/>
+      <c r="O7" s="14" t="inlineStr"/>
+      <c r="P7" s="14" t="inlineStr"/>
+      <c r="Q7" s="14" t="inlineStr"/>
+      <c r="R7" s="14" t="inlineStr"/>
+      <c r="S7" s="14" t="inlineStr"/>
+      <c r="T7" s="14" t="inlineStr"/>
+      <c r="U7" s="14" t="inlineStr"/>
+      <c r="V7" s="14" t="inlineStr"/>
+      <c r="W7" s="14" t="inlineStr"/>
+      <c r="X7" s="14" t="inlineStr"/>
+      <c r="Y7" s="14" t="inlineStr"/>
+      <c r="Z7" s="14" t="inlineStr"/>
+      <c r="AA7" s="14" t="inlineStr"/>
+      <c r="AB7" s="14" t="inlineStr"/>
+      <c r="AC7" s="14" t="inlineStr"/>
+      <c r="AD7" s="14" t="inlineStr"/>
+      <c r="AE7" s="14" t="inlineStr"/>
+      <c r="AF7" s="14" t="inlineStr"/>
+      <c r="AG7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A8" s="10" t="n">
@@ -1856,49 +1835,37 @@
           <t>ตรวจสภาพความพร้อมของมาตราวัดแรงดัน ของก๊าซ CO2 และปรับตั้งอย่างถูกต้อง</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="14" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="14" t="n"/>
-      <c r="N8" s="14" t="n"/>
-      <c r="O8" s="14" t="n"/>
-      <c r="P8" s="14" t="n"/>
-      <c r="Q8" s="14" t="n"/>
-      <c r="R8" s="14" t="n"/>
-      <c r="S8" s="14" t="n"/>
-      <c r="T8" s="14" t="n"/>
-      <c r="U8" s="14" t="n"/>
-      <c r="V8" s="14" t="n"/>
-      <c r="W8" s="14" t="n"/>
-      <c r="X8" s="14" t="n"/>
-      <c r="Y8" s="14" t="n"/>
-      <c r="Z8" s="14" t="n"/>
-      <c r="AA8" s="14" t="n"/>
-      <c r="AB8" s="14" t="n"/>
-      <c r="AC8" s="14" t="n"/>
-      <c r="AD8" s="14" t="n"/>
-      <c r="AE8" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF8" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG8" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C8" s="14" t="inlineStr"/>
+      <c r="D8" s="14" t="inlineStr"/>
+      <c r="E8" s="14" t="inlineStr"/>
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr"/>
+      <c r="J8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
+      <c r="N8" s="14" t="inlineStr"/>
+      <c r="O8" s="14" t="inlineStr"/>
+      <c r="P8" s="14" t="inlineStr"/>
+      <c r="Q8" s="14" t="inlineStr"/>
+      <c r="R8" s="14" t="inlineStr"/>
+      <c r="S8" s="14" t="inlineStr"/>
+      <c r="T8" s="14" t="inlineStr"/>
+      <c r="U8" s="14" t="inlineStr"/>
+      <c r="V8" s="14" t="inlineStr"/>
+      <c r="W8" s="14" t="inlineStr"/>
+      <c r="X8" s="14" t="inlineStr"/>
+      <c r="Y8" s="14" t="inlineStr"/>
+      <c r="Z8" s="14" t="inlineStr"/>
+      <c r="AA8" s="14" t="inlineStr"/>
+      <c r="AB8" s="14" t="inlineStr"/>
+      <c r="AC8" s="14" t="inlineStr"/>
+      <c r="AD8" s="14" t="inlineStr"/>
+      <c r="AE8" s="14" t="inlineStr"/>
+      <c r="AF8" s="14" t="inlineStr"/>
+      <c r="AG8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A9" s="10" t="n">
@@ -1909,49 +1876,37 @@
           <t>ตรวจจุดต่อของก๊าซ CO2 รั่วหรือไม่</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="14" t="n"/>
-      <c r="N9" s="14" t="n"/>
-      <c r="O9" s="14" t="n"/>
-      <c r="P9" s="14" t="n"/>
-      <c r="Q9" s="14" t="n"/>
-      <c r="R9" s="14" t="n"/>
-      <c r="S9" s="14" t="n"/>
-      <c r="T9" s="14" t="n"/>
-      <c r="U9" s="14" t="n"/>
-      <c r="V9" s="14" t="n"/>
-      <c r="W9" s="14" t="n"/>
-      <c r="X9" s="14" t="n"/>
-      <c r="Y9" s="14" t="n"/>
-      <c r="Z9" s="14" t="n"/>
-      <c r="AA9" s="14" t="n"/>
-      <c r="AB9" s="14" t="n"/>
-      <c r="AC9" s="14" t="n"/>
-      <c r="AD9" s="14" t="n"/>
-      <c r="AE9" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C9" s="14" t="inlineStr"/>
+      <c r="D9" s="14" t="inlineStr"/>
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
+      <c r="J9" s="14" t="inlineStr"/>
+      <c r="K9" s="14" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
+      <c r="N9" s="14" t="inlineStr"/>
+      <c r="O9" s="14" t="inlineStr"/>
+      <c r="P9" s="14" t="inlineStr"/>
+      <c r="Q9" s="14" t="inlineStr"/>
+      <c r="R9" s="14" t="inlineStr"/>
+      <c r="S9" s="14" t="inlineStr"/>
+      <c r="T9" s="14" t="inlineStr"/>
+      <c r="U9" s="14" t="inlineStr"/>
+      <c r="V9" s="14" t="inlineStr"/>
+      <c r="W9" s="14" t="inlineStr"/>
+      <c r="X9" s="14" t="inlineStr"/>
+      <c r="Y9" s="14" t="inlineStr"/>
+      <c r="Z9" s="14" t="inlineStr"/>
+      <c r="AA9" s="14" t="inlineStr"/>
+      <c r="AB9" s="14" t="inlineStr"/>
+      <c r="AC9" s="14" t="inlineStr"/>
+      <c r="AD9" s="14" t="inlineStr"/>
+      <c r="AE9" s="14" t="inlineStr"/>
+      <c r="AF9" s="14" t="inlineStr"/>
+      <c r="AG9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A10" s="10" t="n">
@@ -1962,49 +1917,37 @@
           <t>ตรวจสภาพความพร้อมของสายไฟ สายก๊าซ  CO2 ว่ารั่วหรือไม่</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
-      <c r="I10" s="14" t="n"/>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="14" t="n"/>
-      <c r="N10" s="14" t="n"/>
-      <c r="O10" s="14" t="n"/>
-      <c r="P10" s="14" t="n"/>
-      <c r="Q10" s="14" t="n"/>
-      <c r="R10" s="14" t="n"/>
-      <c r="S10" s="14" t="n"/>
-      <c r="T10" s="14" t="n"/>
-      <c r="U10" s="14" t="n"/>
-      <c r="V10" s="14" t="n"/>
-      <c r="W10" s="14" t="n"/>
-      <c r="X10" s="14" t="n"/>
-      <c r="Y10" s="14" t="n"/>
-      <c r="Z10" s="14" t="n"/>
-      <c r="AA10" s="14" t="n"/>
-      <c r="AB10" s="14" t="n"/>
-      <c r="AC10" s="14" t="n"/>
-      <c r="AD10" s="14" t="n"/>
-      <c r="AE10" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C10" s="14" t="inlineStr"/>
+      <c r="D10" s="14" t="inlineStr"/>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr"/>
+      <c r="J10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="inlineStr"/>
+      <c r="L10" s="14" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+      <c r="N10" s="14" t="inlineStr"/>
+      <c r="O10" s="14" t="inlineStr"/>
+      <c r="P10" s="14" t="inlineStr"/>
+      <c r="Q10" s="14" t="inlineStr"/>
+      <c r="R10" s="14" t="inlineStr"/>
+      <c r="S10" s="14" t="inlineStr"/>
+      <c r="T10" s="14" t="inlineStr"/>
+      <c r="U10" s="14" t="inlineStr"/>
+      <c r="V10" s="14" t="inlineStr"/>
+      <c r="W10" s="14" t="inlineStr"/>
+      <c r="X10" s="14" t="inlineStr"/>
+      <c r="Y10" s="14" t="inlineStr"/>
+      <c r="Z10" s="14" t="inlineStr"/>
+      <c r="AA10" s="14" t="inlineStr"/>
+      <c r="AB10" s="14" t="inlineStr"/>
+      <c r="AC10" s="14" t="inlineStr"/>
+      <c r="AD10" s="14" t="inlineStr"/>
+      <c r="AE10" s="14" t="inlineStr"/>
+      <c r="AF10" s="14" t="inlineStr"/>
+      <c r="AG10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A11" s="10" t="n">
@@ -2015,49 +1958,37 @@
           <t>ตรวจสภาพความพร้อมของสายกราวด์</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="14" t="n"/>
-      <c r="I11" s="14" t="n"/>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="14" t="n"/>
-      <c r="N11" s="14" t="n"/>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="14" t="n"/>
-      <c r="Q11" s="14" t="n"/>
-      <c r="R11" s="14" t="n"/>
-      <c r="S11" s="14" t="n"/>
-      <c r="T11" s="14" t="n"/>
-      <c r="U11" s="14" t="n"/>
-      <c r="V11" s="14" t="n"/>
-      <c r="W11" s="14" t="n"/>
-      <c r="X11" s="14" t="n"/>
-      <c r="Y11" s="14" t="n"/>
-      <c r="Z11" s="14" t="n"/>
-      <c r="AA11" s="14" t="n"/>
-      <c r="AB11" s="14" t="n"/>
-      <c r="AC11" s="14" t="n"/>
-      <c r="AD11" s="14" t="n"/>
-      <c r="AE11" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF11" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG11" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C11" s="14" t="inlineStr"/>
+      <c r="D11" s="14" t="inlineStr"/>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr"/>
+      <c r="K11" s="14" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+      <c r="N11" s="14" t="inlineStr"/>
+      <c r="O11" s="14" t="inlineStr"/>
+      <c r="P11" s="14" t="inlineStr"/>
+      <c r="Q11" s="14" t="inlineStr"/>
+      <c r="R11" s="14" t="inlineStr"/>
+      <c r="S11" s="14" t="inlineStr"/>
+      <c r="T11" s="14" t="inlineStr"/>
+      <c r="U11" s="14" t="inlineStr"/>
+      <c r="V11" s="14" t="inlineStr"/>
+      <c r="W11" s="14" t="inlineStr"/>
+      <c r="X11" s="14" t="inlineStr"/>
+      <c r="Y11" s="14" t="inlineStr"/>
+      <c r="Z11" s="14" t="inlineStr"/>
+      <c r="AA11" s="14" t="inlineStr"/>
+      <c r="AB11" s="14" t="inlineStr"/>
+      <c r="AC11" s="14" t="inlineStr"/>
+      <c r="AD11" s="14" t="inlineStr"/>
+      <c r="AE11" s="14" t="inlineStr"/>
+      <c r="AF11" s="14" t="inlineStr"/>
+      <c r="AG11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="11">
       <c r="A12" s="9" t="n">
@@ -2068,96 +1999,72 @@
           <t>ทำความสะอาดหัวเชื่อมก่อนใช้งาน</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="14" t="n"/>
-      <c r="I12" s="14" t="n"/>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14" t="n"/>
-      <c r="N12" s="14" t="n"/>
-      <c r="O12" s="14" t="n"/>
-      <c r="P12" s="14" t="n"/>
-      <c r="Q12" s="14" t="n"/>
-      <c r="R12" s="14" t="n"/>
-      <c r="S12" s="14" t="n"/>
-      <c r="T12" s="14" t="n"/>
-      <c r="U12" s="14" t="n"/>
-      <c r="V12" s="14" t="n"/>
-      <c r="W12" s="14" t="n"/>
-      <c r="X12" s="14" t="n"/>
-      <c r="Y12" s="14" t="n"/>
-      <c r="Z12" s="14" t="n"/>
-      <c r="AA12" s="14" t="n"/>
-      <c r="AB12" s="14" t="n"/>
-      <c r="AC12" s="14" t="n"/>
-      <c r="AD12" s="14" t="n"/>
-      <c r="AE12" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF12" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG12" s="14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr"/>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr"/>
+      <c r="J12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="inlineStr"/>
+      <c r="L12" s="14" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+      <c r="N12" s="14" t="inlineStr"/>
+      <c r="O12" s="14" t="inlineStr"/>
+      <c r="P12" s="14" t="inlineStr"/>
+      <c r="Q12" s="14" t="inlineStr"/>
+      <c r="R12" s="14" t="inlineStr"/>
+      <c r="S12" s="14" t="inlineStr"/>
+      <c r="T12" s="14" t="inlineStr"/>
+      <c r="U12" s="14" t="inlineStr"/>
+      <c r="V12" s="14" t="inlineStr"/>
+      <c r="W12" s="14" t="inlineStr"/>
+      <c r="X12" s="14" t="inlineStr"/>
+      <c r="Y12" s="14" t="inlineStr"/>
+      <c r="Z12" s="14" t="inlineStr"/>
+      <c r="AA12" s="14" t="inlineStr"/>
+      <c r="AB12" s="14" t="inlineStr"/>
+      <c r="AC12" s="14" t="inlineStr"/>
+      <c r="AD12" s="14" t="inlineStr"/>
+      <c r="AE12" s="14" t="inlineStr"/>
+      <c r="AF12" s="14" t="inlineStr"/>
+      <c r="AG12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="7" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="27" t="n"/>
-      <c r="H13" s="27" t="n"/>
-      <c r="I13" s="27" t="n"/>
-      <c r="J13" s="27" t="n"/>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="27" t="n"/>
-      <c r="M13" s="27" t="n"/>
-      <c r="N13" s="27" t="n"/>
-      <c r="O13" s="27" t="n"/>
-      <c r="P13" s="27" t="n"/>
-      <c r="Q13" s="27" t="n"/>
-      <c r="R13" s="27" t="n"/>
-      <c r="S13" s="27" t="n"/>
-      <c r="T13" s="27" t="n"/>
-      <c r="U13" s="27" t="n"/>
-      <c r="V13" s="27" t="n"/>
-      <c r="W13" s="27" t="n"/>
-      <c r="X13" s="27" t="n"/>
-      <c r="Y13" s="27" t="n"/>
-      <c r="Z13" s="27" t="n"/>
-      <c r="AA13" s="39" t="n"/>
-      <c r="AB13" s="27" t="n"/>
-      <c r="AC13" s="27" t="n"/>
-      <c r="AD13" s="27" t="n"/>
-      <c r="AE13" s="39" t="inlineStr">
-        <is>
-          <t>ธนุช สิงห์เถื่อน</t>
-        </is>
-      </c>
-      <c r="AF13" s="39" t="inlineStr">
-        <is>
-          <t>อินทัช เป็นสุข</t>
-        </is>
-      </c>
-      <c r="AG13" s="39" t="inlineStr">
-        <is>
-          <t>อินทัช เป็นสุข</t>
-        </is>
-      </c>
+      <c r="C13" s="27" t="inlineStr"/>
+      <c r="D13" s="27" t="inlineStr"/>
+      <c r="E13" s="27" t="inlineStr"/>
+      <c r="F13" s="27" t="inlineStr"/>
+      <c r="G13" s="27" t="inlineStr"/>
+      <c r="H13" s="27" t="inlineStr"/>
+      <c r="I13" s="27" t="inlineStr"/>
+      <c r="J13" s="27" t="inlineStr"/>
+      <c r="K13" s="27" t="inlineStr"/>
+      <c r="L13" s="27" t="inlineStr"/>
+      <c r="M13" s="27" t="inlineStr"/>
+      <c r="N13" s="27" t="inlineStr"/>
+      <c r="O13" s="27" t="inlineStr"/>
+      <c r="P13" s="27" t="inlineStr"/>
+      <c r="Q13" s="27" t="inlineStr"/>
+      <c r="R13" s="27" t="inlineStr"/>
+      <c r="S13" s="27" t="inlineStr"/>
+      <c r="T13" s="27" t="inlineStr"/>
+      <c r="U13" s="27" t="inlineStr"/>
+      <c r="V13" s="27" t="inlineStr"/>
+      <c r="W13" s="27" t="inlineStr"/>
+      <c r="X13" s="27" t="inlineStr"/>
+      <c r="Y13" s="27" t="inlineStr"/>
+      <c r="Z13" s="27" t="inlineStr"/>
+      <c r="AA13" s="39" t="inlineStr"/>
+      <c r="AB13" s="27" t="inlineStr"/>
+      <c r="AC13" s="27" t="inlineStr"/>
+      <c r="AD13" s="27" t="inlineStr"/>
+      <c r="AE13" s="39" t="inlineStr"/>
+      <c r="AF13" s="39" t="inlineStr"/>
+      <c r="AG13" s="39" t="inlineStr"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="B14" s="6" t="n"/>
@@ -2195,37 +2102,37 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="23" t="n"/>
-      <c r="H15" s="23" t="n"/>
-      <c r="I15" s="23" t="n"/>
-      <c r="J15" s="23" t="n"/>
-      <c r="K15" s="23" t="n"/>
-      <c r="L15" s="23" t="n"/>
-      <c r="M15" s="23" t="n"/>
-      <c r="N15" s="23" t="n"/>
-      <c r="O15" s="23" t="n"/>
-      <c r="P15" s="23" t="n"/>
-      <c r="Q15" s="23" t="n"/>
-      <c r="R15" s="23" t="n"/>
-      <c r="S15" s="23" t="n"/>
-      <c r="T15" s="23" t="n"/>
-      <c r="U15" s="23" t="n"/>
-      <c r="V15" s="23" t="n"/>
-      <c r="W15" s="23" t="n"/>
-      <c r="X15" s="23" t="n"/>
-      <c r="Y15" s="23" t="n"/>
-      <c r="Z15" s="23" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="23" t="n"/>
-      <c r="AC15" s="23" t="n"/>
-      <c r="AD15" s="23" t="n"/>
-      <c r="AE15" s="23" t="n"/>
-      <c r="AF15" s="23" t="n"/>
-      <c r="AG15" s="23" t="n"/>
+      <c r="C15" s="23" t="inlineStr"/>
+      <c r="D15" s="23" t="inlineStr"/>
+      <c r="E15" s="23" t="inlineStr"/>
+      <c r="F15" s="23" t="inlineStr"/>
+      <c r="G15" s="23" t="inlineStr"/>
+      <c r="H15" s="23" t="inlineStr"/>
+      <c r="I15" s="23" t="inlineStr"/>
+      <c r="J15" s="23" t="inlineStr"/>
+      <c r="K15" s="23" t="inlineStr"/>
+      <c r="L15" s="23" t="inlineStr"/>
+      <c r="M15" s="23" t="inlineStr"/>
+      <c r="N15" s="23" t="inlineStr"/>
+      <c r="O15" s="23" t="inlineStr"/>
+      <c r="P15" s="23" t="inlineStr"/>
+      <c r="Q15" s="23" t="inlineStr"/>
+      <c r="R15" s="23" t="inlineStr"/>
+      <c r="S15" s="23" t="inlineStr"/>
+      <c r="T15" s="23" t="inlineStr"/>
+      <c r="U15" s="23" t="inlineStr"/>
+      <c r="V15" s="23" t="inlineStr"/>
+      <c r="W15" s="23" t="inlineStr"/>
+      <c r="X15" s="23" t="inlineStr"/>
+      <c r="Y15" s="23" t="inlineStr"/>
+      <c r="Z15" s="23" t="inlineStr"/>
+      <c r="AA15" s="28" t="inlineStr"/>
+      <c r="AB15" s="23" t="inlineStr"/>
+      <c r="AC15" s="23" t="inlineStr"/>
+      <c r="AD15" s="23" t="inlineStr"/>
+      <c r="AE15" s="23" t="inlineStr"/>
+      <c r="AF15" s="23" t="inlineStr"/>
+      <c r="AG15" s="23" t="inlineStr"/>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="B16" s="6" t="n"/>
@@ -2269,7 +2176,7 @@
       </c>
     </row>
     <row r="18" ht="335.25" customHeight="1">
-      <c r="B18" s="40" t="inlineStr"/>
+      <c r="B18" s="41" t="inlineStr"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="AA19" s="5" t="n"/>

--- a/FM-MN-07_MIG CO2-01.xlsx
+++ b/FM-MN-07_MIG CO2-01.xlsx
@@ -1758,7 +1758,11 @@
       <c r="E6" s="14" t="inlineStr"/>
       <c r="F6" s="14" t="inlineStr"/>
       <c r="G6" s="14" t="inlineStr"/>
-      <c r="H6" s="14" t="inlineStr"/>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="14" t="inlineStr"/>
       <c r="J6" s="14" t="inlineStr"/>
       <c r="K6" s="14" t="inlineStr"/>
@@ -1799,7 +1803,11 @@
       <c r="E7" s="14" t="inlineStr"/>
       <c r="F7" s="14" t="inlineStr"/>
       <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="14" t="inlineStr"/>
       <c r="J7" s="14" t="inlineStr"/>
       <c r="K7" s="14" t="inlineStr"/>
@@ -1840,7 +1848,11 @@
       <c r="E8" s="14" t="inlineStr"/>
       <c r="F8" s="14" t="inlineStr"/>
       <c r="G8" s="14" t="inlineStr"/>
-      <c r="H8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="14" t="inlineStr"/>
       <c r="J8" s="14" t="inlineStr"/>
       <c r="K8" s="14" t="inlineStr"/>
@@ -1881,7 +1893,11 @@
       <c r="E9" s="14" t="inlineStr"/>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr"/>
-      <c r="H9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="14" t="inlineStr"/>
       <c r="J9" s="14" t="inlineStr"/>
       <c r="K9" s="14" t="inlineStr"/>
@@ -1922,7 +1938,11 @@
       <c r="E10" s="14" t="inlineStr"/>
       <c r="F10" s="14" t="inlineStr"/>
       <c r="G10" s="14" t="inlineStr"/>
-      <c r="H10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="14" t="inlineStr"/>
       <c r="J10" s="14" t="inlineStr"/>
       <c r="K10" s="14" t="inlineStr"/>
@@ -1963,7 +1983,11 @@
       <c r="E11" s="14" t="inlineStr"/>
       <c r="F11" s="14" t="inlineStr"/>
       <c r="G11" s="14" t="inlineStr"/>
-      <c r="H11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I11" s="14" t="inlineStr"/>
       <c r="J11" s="14" t="inlineStr"/>
       <c r="K11" s="14" t="inlineStr"/>
@@ -2004,7 +2028,11 @@
       <c r="E12" s="14" t="inlineStr"/>
       <c r="F12" s="14" t="inlineStr"/>
       <c r="G12" s="14" t="inlineStr"/>
-      <c r="H12" s="14" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I12" s="14" t="inlineStr"/>
       <c r="J12" s="14" t="inlineStr"/>
       <c r="K12" s="14" t="inlineStr"/>
@@ -2039,7 +2067,11 @@
       <c r="E13" s="27" t="inlineStr"/>
       <c r="F13" s="27" t="inlineStr"/>
       <c r="G13" s="27" t="inlineStr"/>
-      <c r="H13" s="27" t="inlineStr"/>
+      <c r="H13" s="39" t="inlineStr">
+        <is>
+          <t>อนุสรณ์  ชื่นแฉ่ง</t>
+        </is>
+      </c>
       <c r="I13" s="27" t="inlineStr"/>
       <c r="J13" s="27" t="inlineStr"/>
       <c r="K13" s="27" t="inlineStr"/>

--- a/FM-MN-07_MIG CO2-01.xlsx
+++ b/FM-MN-07_MIG CO2-01.xlsx
@@ -1763,7 +1763,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr"/>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="14" t="inlineStr"/>
       <c r="K6" s="14" t="inlineStr"/>
       <c r="L6" s="14" t="inlineStr"/>
@@ -1808,7 +1812,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="14" t="inlineStr"/>
       <c r="K7" s="14" t="inlineStr"/>
       <c r="L7" s="14" t="inlineStr"/>
@@ -1853,7 +1861,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr"/>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="14" t="inlineStr"/>
       <c r="K8" s="14" t="inlineStr"/>
       <c r="L8" s="14" t="inlineStr"/>
@@ -1898,7 +1910,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="14" t="inlineStr"/>
       <c r="K9" s="14" t="inlineStr"/>
       <c r="L9" s="14" t="inlineStr"/>
@@ -1943,7 +1959,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="14" t="inlineStr"/>
       <c r="K10" s="14" t="inlineStr"/>
       <c r="L10" s="14" t="inlineStr"/>
@@ -1988,7 +2008,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J11" s="14" t="inlineStr"/>
       <c r="K11" s="14" t="inlineStr"/>
       <c r="L11" s="14" t="inlineStr"/>
@@ -2033,7 +2057,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J12" s="14" t="inlineStr"/>
       <c r="K12" s="14" t="inlineStr"/>
       <c r="L12" s="14" t="inlineStr"/>
@@ -2072,7 +2100,11 @@
           <t>อนุสรณ์  ชื่นแฉ่ง</t>
         </is>
       </c>
-      <c r="I13" s="27" t="inlineStr"/>
+      <c r="I13" s="39" t="inlineStr">
+        <is>
+          <t>อนุสรณ์  ชื่นแฉ่ง</t>
+        </is>
+      </c>
       <c r="J13" s="27" t="inlineStr"/>
       <c r="K13" s="27" t="inlineStr"/>
       <c r="L13" s="27" t="inlineStr"/>

--- a/FM-MN-07_MIG CO2-01.xlsx
+++ b/FM-MN-07_MIG CO2-01.xlsx
@@ -1768,7 +1768,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr"/>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="14" t="inlineStr"/>
       <c r="L6" s="14" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -1817,7 +1821,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr"/>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K7" s="14" t="inlineStr"/>
       <c r="L7" s="14" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -1866,7 +1874,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="14" t="inlineStr"/>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="14" t="inlineStr"/>
       <c r="L8" s="14" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -1915,7 +1927,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr"/>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="14" t="inlineStr"/>
       <c r="L9" s="14" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -1964,7 +1980,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr"/>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="14" t="inlineStr"/>
       <c r="L10" s="14" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -2013,7 +2033,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K11" s="14" t="inlineStr"/>
       <c r="L11" s="14" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -2062,7 +2086,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr"/>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K12" s="14" t="inlineStr"/>
       <c r="L12" s="14" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -2105,7 +2133,11 @@
           <t>อนุสรณ์  ชื่นแฉ่ง</t>
         </is>
       </c>
-      <c r="J13" s="27" t="inlineStr"/>
+      <c r="J13" s="39" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
       <c r="K13" s="27" t="inlineStr"/>
       <c r="L13" s="27" t="inlineStr"/>
       <c r="M13" s="27" t="inlineStr"/>

--- a/FM-MN-07_MIG CO2-01.xlsx
+++ b/FM-MN-07_MIG CO2-01.xlsx
@@ -1774,7 +1774,11 @@
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr"/>
-      <c r="L6" s="14" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="14" t="inlineStr"/>
       <c r="N6" s="14" t="inlineStr"/>
       <c r="O6" s="14" t="inlineStr"/>
@@ -1827,7 +1831,11 @@
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr"/>
-      <c r="L7" s="14" t="inlineStr"/>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="14" t="inlineStr"/>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="14" t="inlineStr"/>
@@ -1880,7 +1888,11 @@
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr"/>
-      <c r="L8" s="14" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="14" t="inlineStr"/>
       <c r="N8" s="14" t="inlineStr"/>
       <c r="O8" s="14" t="inlineStr"/>
@@ -1933,7 +1945,11 @@
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr"/>
-      <c r="L9" s="14" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="14" t="inlineStr"/>
       <c r="N9" s="14" t="inlineStr"/>
       <c r="O9" s="14" t="inlineStr"/>
@@ -1986,7 +2002,11 @@
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr"/>
-      <c r="L10" s="14" t="inlineStr"/>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="14" t="inlineStr"/>
       <c r="N10" s="14" t="inlineStr"/>
       <c r="O10" s="14" t="inlineStr"/>
@@ -2039,7 +2059,11 @@
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr"/>
-      <c r="L11" s="14" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M11" s="14" t="inlineStr"/>
       <c r="N11" s="14" t="inlineStr"/>
       <c r="O11" s="14" t="inlineStr"/>
@@ -2092,7 +2116,11 @@
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr"/>
-      <c r="L12" s="14" t="inlineStr"/>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M12" s="14" t="inlineStr"/>
       <c r="N12" s="14" t="inlineStr"/>
       <c r="O12" s="14" t="inlineStr"/>
@@ -2139,7 +2167,11 @@
         </is>
       </c>
       <c r="K13" s="27" t="inlineStr"/>
-      <c r="L13" s="27" t="inlineStr"/>
+      <c r="L13" s="39" t="inlineStr">
+        <is>
+          <t>อนุสรณ์  ชื่นแฉ่ง</t>
+        </is>
+      </c>
       <c r="M13" s="27" t="inlineStr"/>
       <c r="N13" s="27" t="inlineStr"/>
       <c r="O13" s="27" t="inlineStr"/>
